--- a/010-npm_node/02-results/2206JPI02S Anna Waters Creek REV 3 Signage.xlsx
+++ b/010-npm_node/02-results/2206JPI02S Anna Waters Creek REV 3 Signage.xlsx
@@ -464,7 +464,7 @@
         <v>CONTACT</v>
       </c>
       <c r="I2" t="str">
-        <v>CONTRACT_NUMBER</v>
+        <v>CONTRACT</v>
       </c>
       <c r="J2" t="str">
         <v>REVISIONS</v>
@@ -476,7 +476,7 @@
         <v>CONTRACT_FILE</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -504,8 +504,11 @@
       <c r="I3" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J3" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J3" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K3" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -514,7 +517,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -542,8 +545,11 @@
       <c r="I4" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J4" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J4" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K4" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -552,7 +558,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -580,8 +586,11 @@
       <c r="I5" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J5" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J5" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K5" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -590,7 +599,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -618,8 +627,11 @@
       <c r="I6" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J6" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J6" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K6" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -628,7 +640,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -656,8 +668,11 @@
       <c r="I7" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J7" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J7" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K7" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -666,7 +681,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" xml:space="preserve">
       <c r="A8" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -694,8 +709,11 @@
       <c r="I8" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J8" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J8" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K8" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -704,7 +722,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -732,8 +750,11 @@
       <c r="I9" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J9" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J9" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K9" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -742,7 +763,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" xml:space="preserve">
       <c r="A10" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -770,8 +791,11 @@
       <c r="I10" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J10" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J10" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K10" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -780,7 +804,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" xml:space="preserve">
       <c r="A11" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -808,8 +832,11 @@
       <c r="I11" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J11" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J11" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K11" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -818,7 +845,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" xml:space="preserve">
       <c r="A12" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -846,8 +873,11 @@
       <c r="I12" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J12" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J12" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K12" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -856,7 +886,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -884,8 +914,11 @@
       <c r="I13" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J13" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J13" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K13" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -894,7 +927,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" xml:space="preserve">
       <c r="A14" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -922,8 +955,11 @@
       <c r="I14" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J14" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J14" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K14" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -932,7 +968,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" xml:space="preserve">
       <c r="A15" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -960,8 +996,11 @@
       <c r="I15" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J15" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J15" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K15" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -970,7 +1009,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" xml:space="preserve">
       <c r="A16" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -998,8 +1037,11 @@
       <c r="I16" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J16" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J16" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K16" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1008,7 +1050,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" xml:space="preserve">
       <c r="A17" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1036,8 +1078,11 @@
       <c r="I17" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J17" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J17" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K17" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1046,7 +1091,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" xml:space="preserve">
       <c r="A18" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1074,8 +1119,11 @@
       <c r="I18" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J18" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J18" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K18" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1084,7 +1132,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" xml:space="preserve">
       <c r="A19" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1112,8 +1160,11 @@
       <c r="I19" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J19" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J19" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K19" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1122,7 +1173,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" xml:space="preserve">
       <c r="A20" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1150,8 +1201,11 @@
       <c r="I20" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J20" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J20" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K20" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1160,7 +1214,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" xml:space="preserve">
       <c r="A21" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1188,8 +1242,11 @@
       <c r="I21" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J21" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J21" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K21" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1198,7 +1255,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" xml:space="preserve">
       <c r="A22" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1226,8 +1283,11 @@
       <c r="I22" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J22" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J22" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K22" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1236,7 +1296,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" xml:space="preserve">
       <c r="A23" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1264,8 +1324,11 @@
       <c r="I23" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J23" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J23" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K23" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1274,7 +1337,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" xml:space="preserve">
       <c r="A24" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1302,8 +1365,11 @@
       <c r="I24" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J24" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J24" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K24" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1312,7 +1378,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" xml:space="preserve">
       <c r="A25" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1340,8 +1406,11 @@
       <c r="I25" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J25" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J25" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K25" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1350,7 +1419,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" xml:space="preserve">
       <c r="A26" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1378,8 +1447,11 @@
       <c r="I26" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J26" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J26" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K26" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1388,7 +1460,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" xml:space="preserve">
       <c r="A27" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1416,8 +1488,11 @@
       <c r="I27" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J27" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J27" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K27" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1426,7 +1501,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" xml:space="preserve">
       <c r="A28" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1454,8 +1529,11 @@
       <c r="I28" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J28" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J28" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K28" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1464,7 +1542,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" xml:space="preserve">
       <c r="A29" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1492,8 +1570,11 @@
       <c r="I29" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J29" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J29" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K29" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1502,7 +1583,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" xml:space="preserve">
       <c r="A30" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1530,8 +1611,11 @@
       <c r="I30" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J30" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J30" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K30" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1540,7 +1624,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" xml:space="preserve">
       <c r="A31" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1568,8 +1652,11 @@
       <c r="I31" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J31" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J31" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K31" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1578,7 +1665,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" xml:space="preserve">
       <c r="A32" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE </v>
       </c>
@@ -1606,8 +1693,11 @@
       <c r="I32" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J32" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J32" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K32" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1616,7 +1706,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" xml:space="preserve">
       <c r="A33" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE </v>
       </c>
@@ -1644,8 +1734,11 @@
       <c r="I33" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J33" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J33" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K33" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1654,7 +1747,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" xml:space="preserve">
       <c r="A34" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE </v>
       </c>
@@ -1682,8 +1775,11 @@
       <c r="I34" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J34" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J34" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K34" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1692,7 +1788,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" xml:space="preserve">
       <c r="A35" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE </v>
       </c>
@@ -1720,8 +1816,11 @@
       <c r="I35" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J35" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J35" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K35" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1730,7 +1829,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" xml:space="preserve">
       <c r="A36" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE </v>
       </c>
@@ -1758,8 +1857,11 @@
       <c r="I36" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J36" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J36" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K36" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1768,7 +1870,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" xml:space="preserve">
       <c r="A37" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE </v>
       </c>
@@ -1796,8 +1898,11 @@
       <c r="I37" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J37" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J37" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K37" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1806,7 +1911,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" xml:space="preserve">
       <c r="A38" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE </v>
       </c>
@@ -1834,8 +1939,11 @@
       <c r="I38" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J38" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J38" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K38" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1844,7 +1952,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" xml:space="preserve">
       <c r="A39" t="str">
         <v xml:space="preserve">#5: BUILDING MF-1 LEVEL BASEMENT SIGNAGE </v>
       </c>
@@ -1872,8 +1980,11 @@
       <c r="I39" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J39" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J39" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K39" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1882,7 +1993,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" xml:space="preserve">
       <c r="A40" t="str">
         <v xml:space="preserve">#5: BUILDING MF-1 LEVEL BASEMENT SIGNAGE </v>
       </c>
@@ -1910,8 +2021,11 @@
       <c r="I40" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J40" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J40" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K40" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1920,7 +2034,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" xml:space="preserve">
       <c r="A41" t="str">
         <v xml:space="preserve">#5: BUILDING MF-1 LEVEL BASEMENT SIGNAGE </v>
       </c>
@@ -1948,8 +2062,11 @@
       <c r="I41" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J41" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J41" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K41" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1958,7 +2075,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" xml:space="preserve">
       <c r="A42" t="str">
         <v xml:space="preserve">#5: BUILDING MF-1 LEVEL BASEMENT SIGNAGE </v>
       </c>
@@ -1986,8 +2103,11 @@
       <c r="I42" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J42" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J42" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K42" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -1996,7 +2116,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" xml:space="preserve">
       <c r="A43" t="str">
         <v xml:space="preserve">#5: BUILDING MF-1 LEVEL BASEMENT SIGNAGE </v>
       </c>
@@ -2024,8 +2144,11 @@
       <c r="I43" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J43" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J43" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K43" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2034,7 +2157,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" xml:space="preserve">
       <c r="A44" t="str">
         <v xml:space="preserve">#5: BUILDING MF-1 LEVEL BASEMENT SIGNAGE </v>
       </c>
@@ -2062,8 +2185,11 @@
       <c r="I44" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J44" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J44" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K44" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2072,7 +2198,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" xml:space="preserve">
       <c r="A45" t="str">
         <v xml:space="preserve">#5: BUILDING MF-1 LEVEL BASEMENT SIGNAGE </v>
       </c>
@@ -2100,8 +2226,11 @@
       <c r="I45" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J45" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J45" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K45" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2110,7 +2239,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" xml:space="preserve">
       <c r="A46" t="str">
         <v xml:space="preserve">#5: BUILDING MF-1 LEVEL BASEMENT SIGNAGE </v>
       </c>
@@ -2138,8 +2267,11 @@
       <c r="I46" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J46" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J46" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K46" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2148,7 +2280,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" xml:space="preserve">
       <c r="A47" t="str">
         <v xml:space="preserve">#5: BUILDING MF-1 LEVEL BASEMENT SIGNAGE </v>
       </c>
@@ -2176,8 +2308,11 @@
       <c r="I47" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J47" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J47" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K47" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2186,7 +2321,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" xml:space="preserve">
       <c r="A48" t="str">
         <v xml:space="preserve">#6: BUILDING MF-1 LEVEL 1 SIGNAGE </v>
       </c>
@@ -2214,8 +2349,11 @@
       <c r="I48" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J48" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J48" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K48" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2224,7 +2362,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" xml:space="preserve">
       <c r="A49" t="str">
         <v xml:space="preserve">#6: BUILDING MF-1 LEVEL 1 SIGNAGE </v>
       </c>
@@ -2252,8 +2390,11 @@
       <c r="I49" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J49" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J49" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K49" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2262,7 +2403,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" xml:space="preserve">
       <c r="A50" t="str">
         <v xml:space="preserve">#6: BUILDING MF-1 LEVEL 1 SIGNAGE </v>
       </c>
@@ -2290,8 +2431,11 @@
       <c r="I50" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J50" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J50" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K50" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2300,7 +2444,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" xml:space="preserve">
       <c r="A51" t="str">
         <v xml:space="preserve">#6: BUILDING MF-1 LEVEL 1 SIGNAGE </v>
       </c>
@@ -2328,8 +2472,11 @@
       <c r="I51" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J51" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J51" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K51" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2338,7 +2485,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" xml:space="preserve">
       <c r="A52" t="str">
         <v xml:space="preserve">#6: BUILDING MF-1 LEVEL 1 SIGNAGE </v>
       </c>
@@ -2366,8 +2513,11 @@
       <c r="I52" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J52" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J52" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K52" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2376,7 +2526,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" xml:space="preserve">
       <c r="A53" t="str">
         <v xml:space="preserve">#6: BUILDING MF-1 LEVEL 1 SIGNAGE </v>
       </c>
@@ -2404,8 +2554,11 @@
       <c r="I53" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J53" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J53" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K53" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2414,7 +2567,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" xml:space="preserve">
       <c r="A54" t="str">
         <v xml:space="preserve">#6: BUILDING MF-1 LEVEL 1 SIGNAGE </v>
       </c>
@@ -2442,8 +2595,11 @@
       <c r="I54" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J54" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J54" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K54" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2452,7 +2608,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" xml:space="preserve">
       <c r="A55" t="str">
         <v xml:space="preserve">#6: BUILDING MF-1 LEVEL 1 SIGNAGE </v>
       </c>
@@ -2480,8 +2636,11 @@
       <c r="I55" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J55" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J55" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K55" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2490,7 +2649,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" xml:space="preserve">
       <c r="A56" t="str">
         <v xml:space="preserve">#6: BUILDING MF-1 LEVEL 1 SIGNAGE </v>
       </c>
@@ -2518,8 +2677,11 @@
       <c r="I56" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J56" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J56" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K56" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2528,7 +2690,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" xml:space="preserve">
       <c r="A57" t="str">
         <v xml:space="preserve">#6: BUILDING MF-1 LEVEL 1 SIGNAGE </v>
       </c>
@@ -2556,8 +2718,11 @@
       <c r="I57" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J57" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J57" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K57" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2566,7 +2731,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" xml:space="preserve">
       <c r="A58" t="str">
         <v xml:space="preserve">#7: BUILDING MF-1 LEVEL 2 SIGNAGE </v>
       </c>
@@ -2594,8 +2759,11 @@
       <c r="I58" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J58" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J58" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K58" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2604,7 +2772,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" xml:space="preserve">
       <c r="A59" t="str">
         <v xml:space="preserve">#7: BUILDING MF-1 LEVEL 2 SIGNAGE </v>
       </c>
@@ -2632,8 +2800,11 @@
       <c r="I59" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J59" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J59" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K59" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2642,7 +2813,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" xml:space="preserve">
       <c r="A60" t="str">
         <v xml:space="preserve">#7: BUILDING MF-1 LEVEL 2 SIGNAGE </v>
       </c>
@@ -2670,8 +2841,11 @@
       <c r="I60" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J60" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J60" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K60" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2680,7 +2854,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" xml:space="preserve">
       <c r="A61" t="str">
         <v xml:space="preserve">#7: BUILDING MF-1 LEVEL 2 SIGNAGE </v>
       </c>
@@ -2708,8 +2882,11 @@
       <c r="I61" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J61" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J61" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K61" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2718,7 +2895,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" xml:space="preserve">
       <c r="A62" t="str">
         <v xml:space="preserve">#7: BUILDING MF-1 LEVEL 2 SIGNAGE </v>
       </c>
@@ -2746,8 +2923,11 @@
       <c r="I62" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J62" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J62" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K62" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2756,7 +2936,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" xml:space="preserve">
       <c r="A63" t="str">
         <v xml:space="preserve">#7: BUILDING MF-1 LEVEL 2 SIGNAGE </v>
       </c>
@@ -2784,8 +2964,11 @@
       <c r="I63" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J63" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J63" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K63" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2794,7 +2977,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" xml:space="preserve">
       <c r="A64" t="str">
         <v xml:space="preserve">#7: BUILDING MF-1 LEVEL 2 SIGNAGE </v>
       </c>
@@ -2822,8 +3005,11 @@
       <c r="I64" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J64" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J64" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K64" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2832,7 +3018,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" xml:space="preserve">
       <c r="A65" t="str">
         <v xml:space="preserve">#7: BUILDING MF-1 LEVEL 2 SIGNAGE </v>
       </c>
@@ -2860,8 +3046,11 @@
       <c r="I65" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J65" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J65" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K65" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2870,7 +3059,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" xml:space="preserve">
       <c r="A66" t="str">
         <v xml:space="preserve">#8: BUILDING MF-1 LEVEL 3 SIGNAGE </v>
       </c>
@@ -2898,8 +3087,11 @@
       <c r="I66" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J66" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J66" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K66" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2908,7 +3100,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" xml:space="preserve">
       <c r="A67" t="str">
         <v xml:space="preserve">#8: BUILDING MF-1 LEVEL 3 SIGNAGE </v>
       </c>
@@ -2936,8 +3128,11 @@
       <c r="I67" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J67" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J67" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K67" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2946,7 +3141,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" xml:space="preserve">
       <c r="A68" t="str">
         <v xml:space="preserve">#8: BUILDING MF-1 LEVEL 3 SIGNAGE </v>
       </c>
@@ -2974,8 +3169,11 @@
       <c r="I68" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J68" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J68" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K68" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -2984,7 +3182,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" xml:space="preserve">
       <c r="A69" t="str">
         <v xml:space="preserve">#8: BUILDING MF-1 LEVEL 3 SIGNAGE </v>
       </c>
@@ -3012,8 +3210,11 @@
       <c r="I69" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J69" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J69" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K69" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3022,7 +3223,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" xml:space="preserve">
       <c r="A70" t="str">
         <v xml:space="preserve">#8: BUILDING MF-1 LEVEL 3 SIGNAGE </v>
       </c>
@@ -3050,8 +3251,11 @@
       <c r="I70" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J70" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J70" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K70" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3060,7 +3264,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" xml:space="preserve">
       <c r="A71" t="str">
         <v xml:space="preserve">#8: BUILDING MF-1 LEVEL 3 SIGNAGE </v>
       </c>
@@ -3088,8 +3292,11 @@
       <c r="I71" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J71" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J71" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K71" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3098,7 +3305,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" xml:space="preserve">
       <c r="A72" t="str">
         <v xml:space="preserve">#8: BUILDING MF-1 LEVEL 3 SIGNAGE </v>
       </c>
@@ -3126,8 +3333,11 @@
       <c r="I72" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J72" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J72" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K72" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3136,7 +3346,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" xml:space="preserve">
       <c r="A73" t="str">
         <v xml:space="preserve">#8: BUILDING MF-1 LEVEL 3 SIGNAGE </v>
       </c>
@@ -3164,8 +3374,11 @@
       <c r="I73" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J73" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J73" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K73" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3174,7 +3387,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" xml:space="preserve">
       <c r="A74" t="str">
         <v xml:space="preserve">#9: BUILDING MF-1 LEVEL 4 SIGNAGE </v>
       </c>
@@ -3202,8 +3415,11 @@
       <c r="I74" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J74" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J74" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K74" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3212,7 +3428,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" xml:space="preserve">
       <c r="A75" t="str">
         <v xml:space="preserve">#9: BUILDING MF-1 LEVEL 4 SIGNAGE </v>
       </c>
@@ -3240,8 +3456,11 @@
       <c r="I75" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J75" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J75" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K75" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3250,7 +3469,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" xml:space="preserve">
       <c r="A76" t="str">
         <v xml:space="preserve">#9: BUILDING MF-1 LEVEL 4 SIGNAGE </v>
       </c>
@@ -3278,8 +3497,11 @@
       <c r="I76" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J76" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J76" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K76" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3288,7 +3510,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" xml:space="preserve">
       <c r="A77" t="str">
         <v xml:space="preserve">#9: BUILDING MF-1 LEVEL 4 SIGNAGE </v>
       </c>
@@ -3316,8 +3538,11 @@
       <c r="I77" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J77" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J77" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K77" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3326,7 +3551,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" xml:space="preserve">
       <c r="A78" t="str">
         <v xml:space="preserve">#9: BUILDING MF-1 LEVEL 4 SIGNAGE </v>
       </c>
@@ -3354,8 +3579,11 @@
       <c r="I78" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J78" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J78" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K78" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3364,7 +3592,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" xml:space="preserve">
       <c r="A79" t="str">
         <v xml:space="preserve">#9: BUILDING MF-1 LEVEL 4 SIGNAGE </v>
       </c>
@@ -3392,8 +3620,11 @@
       <c r="I79" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J79" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J79" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K79" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3402,7 +3633,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" xml:space="preserve">
       <c r="A80" t="str">
         <v xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </v>
       </c>
@@ -3430,8 +3661,11 @@
       <c r="I80" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J80" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J80" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K80" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3440,7 +3674,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" xml:space="preserve">
       <c r="A81" t="str">
         <v xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </v>
       </c>
@@ -3468,8 +3702,11 @@
       <c r="I81" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J81" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J81" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K81" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3478,7 +3715,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" xml:space="preserve">
       <c r="A82" t="str">
         <v xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </v>
       </c>
@@ -3506,8 +3743,11 @@
       <c r="I82" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J82" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J82" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K82" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3516,7 +3756,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" xml:space="preserve">
       <c r="A83" t="str">
         <v xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </v>
       </c>
@@ -3544,8 +3784,11 @@
       <c r="I83" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J83" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J83" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K83" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3554,7 +3797,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" xml:space="preserve">
       <c r="A84" t="str">
         <v xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </v>
       </c>
@@ -3582,8 +3825,11 @@
       <c r="I84" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J84" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J84" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K84" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3592,7 +3838,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" xml:space="preserve">
       <c r="A85" t="str">
         <v xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </v>
       </c>
@@ -3620,8 +3866,11 @@
       <c r="I85" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J85" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J85" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K85" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3630,7 +3879,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" xml:space="preserve">
       <c r="A86" t="str">
         <v xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </v>
       </c>
@@ -3658,8 +3907,11 @@
       <c r="I86" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J86" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J86" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K86" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3668,7 +3920,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" xml:space="preserve">
       <c r="A87" t="str">
         <v xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </v>
       </c>
@@ -3696,8 +3948,11 @@
       <c r="I87" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J87" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J87" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K87" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3706,7 +3961,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" xml:space="preserve">
       <c r="A88" t="str">
         <v xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </v>
       </c>
@@ -3734,8 +3989,11 @@
       <c r="I88" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J88" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J88" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K88" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3744,7 +4002,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" xml:space="preserve">
       <c r="A89" t="str">
         <v xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </v>
       </c>
@@ -3772,8 +4030,11 @@
       <c r="I89" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J89" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J89" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K89" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3782,7 +4043,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" xml:space="preserve">
       <c r="A90" t="str">
         <v xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </v>
       </c>
@@ -3810,8 +4071,11 @@
       <c r="I90" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J90" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J90" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K90" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3820,7 +4084,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" xml:space="preserve">
       <c r="A91" t="str">
         <v xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </v>
       </c>
@@ -3848,8 +4112,11 @@
       <c r="I91" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J91" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J91" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K91" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3858,7 +4125,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" xml:space="preserve">
       <c r="A92" t="str">
         <v xml:space="preserve">#11: BUILDING MF-2 LEVEL 2 SIGNAGE </v>
       </c>
@@ -3886,8 +4153,11 @@
       <c r="I92" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J92" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J92" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K92" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3896,7 +4166,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" xml:space="preserve">
       <c r="A93" t="str">
         <v xml:space="preserve">#11: BUILDING MF-2 LEVEL 2 SIGNAGE </v>
       </c>
@@ -3924,8 +4194,11 @@
       <c r="I93" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J93" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J93" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K93" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3934,7 +4207,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" xml:space="preserve">
       <c r="A94" t="str">
         <v xml:space="preserve">#11: BUILDING MF-2 LEVEL 2 SIGNAGE </v>
       </c>
@@ -3962,8 +4235,11 @@
       <c r="I94" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J94" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J94" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K94" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -3972,7 +4248,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" xml:space="preserve">
       <c r="A95" t="str">
         <v xml:space="preserve">#11: BUILDING MF-2 LEVEL 2 SIGNAGE </v>
       </c>
@@ -4000,8 +4276,11 @@
       <c r="I95" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J95" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J95" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K95" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4010,7 +4289,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" xml:space="preserve">
       <c r="A96" t="str">
         <v xml:space="preserve">#11: BUILDING MF-2 LEVEL 2 SIGNAGE </v>
       </c>
@@ -4038,8 +4317,11 @@
       <c r="I96" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J96" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J96" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K96" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4048,7 +4330,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" xml:space="preserve">
       <c r="A97" t="str">
         <v xml:space="preserve">#11: BUILDING MF-2 LEVEL 2 SIGNAGE </v>
       </c>
@@ -4076,8 +4358,11 @@
       <c r="I97" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J97" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J97" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K97" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4086,7 +4371,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" xml:space="preserve">
       <c r="A98" t="str">
         <v xml:space="preserve">#11: BUILDING MF-2 LEVEL 2 SIGNAGE </v>
       </c>
@@ -4114,8 +4399,11 @@
       <c r="I98" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J98" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J98" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K98" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4124,7 +4412,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" xml:space="preserve">
       <c r="A99" t="str">
         <v xml:space="preserve">#11: BUILDING MF-2 LEVEL 2 SIGNAGE </v>
       </c>
@@ -4152,8 +4440,11 @@
       <c r="I99" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J99" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J99" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K99" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4162,7 +4453,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" xml:space="preserve">
       <c r="A100" t="str">
         <v xml:space="preserve">#11: BUILDING MF-2 LEVEL 2 SIGNAGE </v>
       </c>
@@ -4190,8 +4481,11 @@
       <c r="I100" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J100" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J100" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K100" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4200,7 +4494,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" xml:space="preserve">
       <c r="A101" t="str">
         <v xml:space="preserve">#12: BUILDING MF-2 LEVEL 3 SIGNAGE </v>
       </c>
@@ -4228,8 +4522,11 @@
       <c r="I101" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J101" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J101" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K101" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4238,7 +4535,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" xml:space="preserve">
       <c r="A102" t="str">
         <v xml:space="preserve">#12: BUILDING MF-2 LEVEL 3 SIGNAGE </v>
       </c>
@@ -4266,8 +4563,11 @@
       <c r="I102" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J102" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J102" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K102" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4276,7 +4576,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" xml:space="preserve">
       <c r="A103" t="str">
         <v xml:space="preserve">#12: BUILDING MF-2 LEVEL 3 SIGNAGE </v>
       </c>
@@ -4304,8 +4604,11 @@
       <c r="I103" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J103" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J103" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K103" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4314,7 +4617,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" xml:space="preserve">
       <c r="A104" t="str">
         <v xml:space="preserve">#12: BUILDING MF-2 LEVEL 3 SIGNAGE </v>
       </c>
@@ -4342,8 +4645,11 @@
       <c r="I104" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J104" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J104" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K104" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4352,7 +4658,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" xml:space="preserve">
       <c r="A105" t="str">
         <v xml:space="preserve">#12: BUILDING MF-2 LEVEL 3 SIGNAGE </v>
       </c>
@@ -4380,8 +4686,11 @@
       <c r="I105" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J105" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J105" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K105" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4390,7 +4699,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" xml:space="preserve">
       <c r="A106" t="str">
         <v xml:space="preserve">#12: BUILDING MF-2 LEVEL 3 SIGNAGE </v>
       </c>
@@ -4418,8 +4727,11 @@
       <c r="I106" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J106" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J106" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K106" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4428,7 +4740,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" xml:space="preserve">
       <c r="A107" t="str">
         <v xml:space="preserve">#12: BUILDING MF-2 LEVEL 3 SIGNAGE </v>
       </c>
@@ -4456,8 +4768,11 @@
       <c r="I107" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J107" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J107" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K107" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4466,7 +4781,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" xml:space="preserve">
       <c r="A108" t="str">
         <v xml:space="preserve">#13: BUILDING MF-2 LEVEL 4 SIGNAGE </v>
       </c>
@@ -4494,8 +4809,11 @@
       <c r="I108" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J108" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J108" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K108" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4504,7 +4822,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" xml:space="preserve">
       <c r="A109" t="str">
         <v xml:space="preserve">#13: BUILDING MF-2 LEVEL 4 SIGNAGE </v>
       </c>
@@ -4532,8 +4850,11 @@
       <c r="I109" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J109" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J109" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K109" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4542,7 +4863,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" xml:space="preserve">
       <c r="A110" t="str">
         <v xml:space="preserve">#13: BUILDING MF-2 LEVEL 4 SIGNAGE </v>
       </c>
@@ -4570,8 +4891,11 @@
       <c r="I110" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J110" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J110" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K110" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4580,7 +4904,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" xml:space="preserve">
       <c r="A111" t="str">
         <v xml:space="preserve">#13: BUILDING MF-2 LEVEL 4 SIGNAGE </v>
       </c>
@@ -4608,8 +4932,11 @@
       <c r="I111" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J111" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J111" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K111" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4618,7 +4945,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" xml:space="preserve">
       <c r="A112" t="str">
         <v xml:space="preserve">#13: BUILDING MF-2 LEVEL 4 SIGNAGE </v>
       </c>
@@ -4646,8 +4973,11 @@
       <c r="I112" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J112" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J112" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K112" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4656,7 +4986,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" xml:space="preserve">
       <c r="A113" t="str">
         <v xml:space="preserve">#13: BUILDING MF-2 LEVEL 4 SIGNAGE </v>
       </c>
@@ -4684,8 +5014,11 @@
       <c r="I113" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J113" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J113" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K113" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4694,7 +5027,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" xml:space="preserve">
       <c r="A114" t="str">
         <v xml:space="preserve">#13: BUILDING MF-2 LEVEL 4 SIGNAGE </v>
       </c>
@@ -4722,8 +5055,11 @@
       <c r="I114" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J114" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J114" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K114" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4732,7 +5068,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" xml:space="preserve">
       <c r="A115" t="str">
         <v xml:space="preserve">#13: BUILDING MF-2 LEVEL 4 SIGNAGE </v>
       </c>
@@ -4760,8 +5096,11 @@
       <c r="I115" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J115" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J115" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K115" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4770,7 +5109,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" xml:space="preserve">
       <c r="A116" t="str">
         <v xml:space="preserve">#14: BUILDING MF-3 SIGNAGE </v>
       </c>
@@ -4798,8 +5137,11 @@
       <c r="I116" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J116" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J116" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K116" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4808,7 +5150,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" xml:space="preserve">
       <c r="A117" t="str">
         <v xml:space="preserve">#14: BUILDING MF-3 SIGNAGE </v>
       </c>
@@ -4836,8 +5178,11 @@
       <c r="I117" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J117" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J117" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K117" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4846,7 +5191,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" xml:space="preserve">
       <c r="A118" t="str">
         <v xml:space="preserve">#14: BUILDING MF-3 SIGNAGE </v>
       </c>
@@ -4874,8 +5219,11 @@
       <c r="I118" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J118" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J118" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K118" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4884,7 +5232,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" xml:space="preserve">
       <c r="A119" t="str">
         <v xml:space="preserve">#14: BUILDING MF-3 SIGNAGE </v>
       </c>
@@ -4912,8 +5260,11 @@
       <c r="I119" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J119" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J119" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K119" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4922,7 +5273,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" xml:space="preserve">
       <c r="A120" t="str">
         <v xml:space="preserve">#14: BUILDING MF-3 SIGNAGE </v>
       </c>
@@ -4950,8 +5301,11 @@
       <c r="I120" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J120" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J120" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K120" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4960,7 +5314,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" xml:space="preserve">
       <c r="A121" t="str">
         <v xml:space="preserve">#14: BUILDING MF-3 SIGNAGE </v>
       </c>
@@ -4988,8 +5342,11 @@
       <c r="I121" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J121" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J121" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K121" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -4998,7 +5355,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" xml:space="preserve">
       <c r="A122" t="str">
         <v xml:space="preserve">#15: AMENITY SIGNAGE </v>
       </c>
@@ -5026,8 +5383,11 @@
       <c r="I122" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J122" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J122" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K122" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -5036,7 +5396,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" xml:space="preserve">
       <c r="A123" t="str">
         <v xml:space="preserve">#15: AMENITY SIGNAGE </v>
       </c>
@@ -5064,8 +5424,11 @@
       <c r="I123" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J123" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J123" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K123" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -5074,7 +5437,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" xml:space="preserve">
       <c r="A124" t="str">
         <v xml:space="preserve">#15: AMENITY SIGNAGE </v>
       </c>
@@ -5102,8 +5465,11 @@
       <c r="I124" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J124" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J124" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K124" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -5112,7 +5478,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" xml:space="preserve">
       <c r="A125" t="str">
         <v xml:space="preserve">#15: AMENITY SIGNAGE </v>
       </c>
@@ -5140,8 +5506,11 @@
       <c r="I125" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J125" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J125" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K125" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -5150,7 +5519,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" xml:space="preserve">
       <c r="A126" t="str">
         <v xml:space="preserve">#15: AMENITY SIGNAGE </v>
       </c>
@@ -5178,8 +5547,11 @@
       <c r="I126" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J126" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J126" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K126" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -5188,7 +5560,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" xml:space="preserve">
       <c r="A127" t="str">
         <v xml:space="preserve">#15: AMENITY SIGNAGE </v>
       </c>
@@ -5216,8 +5588,11 @@
       <c r="I127" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J127" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J127" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K127" t="str">
         <v>ANNA WATERS CREEK</v>
@@ -5226,7 +5601,7 @@
         <v>2206JPI02S Anna Waters Creek REV 3 Signage.xlsx</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" xml:space="preserve">
       <c r="A128" t="str">
         <v xml:space="preserve">#15: AMENITY SIGNAGE </v>
       </c>
@@ -5254,8 +5629,11 @@
       <c r="I128" t="str">
         <v>2206JPI02S</v>
       </c>
-      <c r="J128" t="str">
-        <v>10.13.22 11.20.23 REV 1 11.29.23 REV 2 4.08.24 Rev 3</v>
+      <c r="J128" t="str" xml:space="preserve">
+        <v xml:space="preserve">10.13.22 11.20.23 REV 1
+ 11.29.23 REV 2
+ 4.08.24 Rev 3
+</v>
       </c>
       <c r="K128" t="str">
         <v>ANNA WATERS CREEK</v>
